--- a/branches/feat/instance-validation/all-profiles.xlsx
+++ b/branches/feat/instance-validation/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:19:42+00:00</t>
+    <t>2026-09-09T13:12:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/instance-validation/all-profiles.xlsx
+++ b/branches/feat/instance-validation/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:12:03+00:00</t>
+    <t>2026-09-09T18:27:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
